--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohdn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{494C633A-28B9-419F-B0AC-4F3C0A1A317B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t xml:space="preserve">good </t>
+  </si>
+  <si>
+    <t>learn new things</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1299,7 @@
         <v>420</v>
       </c>
       <c r="C12" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
         <v>420</v>
@@ -1315,11 +1318,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>56</v>
@@ -1335,26 +1338,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="14">
+        <v>440</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>160</v>
+      </c>
+      <c r="E13" s="14">
+        <v>180</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>200</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{494C633A-28B9-419F-B0AC-4F3C0A1A317B}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{114501F2-1948-418A-BD1F-A34AE3F039EC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -517,6 +517,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1384,26 +1388,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>300</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohdn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{114501F2-1948-418A-BD1F-A34AE3F039EC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,9 +233,6 @@
   </si>
   <si>
     <t xml:space="preserve">good </t>
-  </si>
-  <si>
-    <t>learn new things</t>
   </si>
 </sst>
 </file>
@@ -517,10 +514,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1303,7 +1296,7 @@
         <v>420</v>
       </c>
       <c r="C12" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D12" s="14">
         <v>420</v>
@@ -1322,11 +1315,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1430</v>
+        <v>1440</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>56</v>
@@ -1342,96 +1335,48 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
-        <v>46259</v>
-      </c>
-      <c r="B13" s="14">
-        <v>440</v>
-      </c>
-      <c r="C13" s="14">
-        <v>30</v>
-      </c>
-      <c r="D13" s="14">
-        <v>160</v>
-      </c>
-      <c r="E13" s="14">
-        <v>180</v>
-      </c>
-      <c r="F13" s="14">
-        <v>350</v>
-      </c>
-      <c r="G13" s="14">
-        <v>7</v>
-      </c>
-      <c r="H13" s="14">
-        <v>200</v>
-      </c>
-      <c r="I13" s="15">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1360</v>
-      </c>
-      <c r="J13" s="15">
+        <v/>
+      </c>
+      <c r="J13" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>66</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
-        <v>46260</v>
-      </c>
-      <c r="B14" s="14">
-        <v>420</v>
-      </c>
-      <c r="C14" s="14">
-        <v>20</v>
-      </c>
-      <c r="D14" s="14">
-        <v>180</v>
-      </c>
-      <c r="E14" s="14">
-        <v>60</v>
-      </c>
-      <c r="F14" s="14">
-        <v>200</v>
-      </c>
-      <c r="G14" s="14">
-        <v>4</v>
-      </c>
-      <c r="H14" s="14">
-        <v>300</v>
-      </c>
-      <c r="I14" s="15">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1180</v>
-      </c>
-      <c r="J14" s="15">
+        <v/>
+      </c>
+      <c r="J14" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>60</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/xl sheet (1).xlsx
+++ b/xl sheet (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohdn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C33C936A-2739-49E5-A3CA-3B6A2C8785A4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,27 @@
   </si>
   <si>
     <t xml:space="preserve">good </t>
+  </si>
+  <si>
+    <t>learn new things</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good </t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>Good day</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -514,6 +535,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1296,7 +1321,7 @@
         <v>420</v>
       </c>
       <c r="C12" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
         <v>420</v>
@@ -1315,11 +1340,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>56</v>
@@ -1335,224 +1360,464 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="14">
+        <v>440</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>160</v>
+      </c>
+      <c r="E13" s="14">
+        <v>180</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>200</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>300</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="14">
+        <v>440</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>200</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>130</v>
+      </c>
+      <c r="E16" s="14">
+        <v>150</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>250</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="14">
+        <v>460</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>250</v>
+      </c>
+      <c r="E17" s="14">
+        <v>210</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>253</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1193</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>247</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="14">
+        <v>460</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>230</v>
+      </c>
+      <c r="E18" s="14">
+        <v>180</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>310</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>410</v>
+      </c>
+      <c r="E19" s="14">
+        <v>100</v>
+      </c>
+      <c r="F19" s="14">
+        <v>100</v>
+      </c>
+      <c r="G19" s="14">
+        <v>2</v>
+      </c>
+      <c r="H19" s="14">
+        <v>375</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1435</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>5</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>40</v>
+      </c>
+      <c r="D20" s="14">
+        <v>200</v>
+      </c>
+      <c r="E20" s="14">
+        <v>120</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>20</v>
+      </c>
+      <c r="D21" s="14">
+        <v>240</v>
+      </c>
+      <c r="E21" s="14">
+        <v>130</v>
+      </c>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>250</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B22" s="14">
+        <v>400</v>
+      </c>
+      <c r="C22" s="14">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <v>150</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>200</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
